--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD516BDD-31BD-463B-B138-AC440F31202D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B734CC65-CE61-4CE6-8427-45786A4ED982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3000" yWindow="345" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="47">
   <si>
     <t>Company Name</t>
   </si>
@@ -4640,154 +4640,82 @@
         <v>40</v>
       </c>
       <c r="C146">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D146" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H146" s="2">
+        <v>7.9861111111111105E-3</v>
+      </c>
+      <c r="I146" s="1">
+        <v>46176.425347222219</v>
+      </c>
+      <c r="J146">
         <v>0</v>
-      </c>
-      <c r="I146" s="1">
-        <v>46146.730208333334</v>
-      </c>
-      <c r="J146">
-        <v>1</v>
       </c>
       <c r="K146" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F147" s="2"/>
-      <c r="G147" s="1"/>
-      <c r="H147" s="2"/>
-      <c r="I147" s="1"/>
+      <c r="B147" t="s">
+        <v>40</v>
+      </c>
+      <c r="C147">
+        <v>679</v>
+      </c>
+      <c r="D147" t="s">
+        <v>45</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="2">
+        <v>7.743055555555556E-3</v>
+      </c>
+      <c r="I147" s="1">
+        <v>46176.425347222219</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
       <c r="K147" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>40</v>
-      </c>
-      <c r="C148">
-        <v>678</v>
-      </c>
-      <c r="D148" t="s">
-        <v>41</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H148" s="2">
-        <v>0</v>
-      </c>
-      <c r="I148" s="1">
-        <v>46176.42465277778</v>
-      </c>
-      <c r="J148">
-        <v>1</v>
-      </c>
-      <c r="K148" t="s">
-        <v>11</v>
-      </c>
+      <c r="F148" s="2"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="1"/>
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B149" t="s">
-        <v>40</v>
-      </c>
-      <c r="C149">
-        <v>680</v>
-      </c>
-      <c r="D149" t="s">
-        <v>42</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H149" s="2">
-        <v>7.9861111111111105E-3</v>
-      </c>
-      <c r="I149" s="1">
-        <v>46176.425347222219</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149" t="s">
-        <v>11</v>
-      </c>
+      <c r="F149" s="2"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="1"/>
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B150" t="s">
-        <v>40</v>
-      </c>
-      <c r="C150">
-        <v>676</v>
-      </c>
-      <c r="D150" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H150" s="2">
-        <v>0</v>
-      </c>
-      <c r="I150" s="1">
-        <v>46176.425347222219</v>
-      </c>
-      <c r="J150">
-        <v>1</v>
-      </c>
-      <c r="K150" t="s">
-        <v>11</v>
-      </c>
+      <c r="F150" s="2"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="1"/>
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B151" t="s">
-        <v>40</v>
-      </c>
-      <c r="C151">
-        <v>679</v>
-      </c>
-      <c r="D151" t="s">
-        <v>45</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H151" s="2">
-        <v>7.743055555555556E-3</v>
-      </c>
-      <c r="I151" s="1">
-        <v>46176.425347222219</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151" t="s">
-        <v>11</v>
-      </c>
+      <c r="F151" s="2"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="1"/>
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F152" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B734CC65-CE61-4CE6-8427-45786A4ED982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685EDF14-735D-4E12-B3E4-05CE29297531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="345" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="47">
   <si>
     <t>Company Name</t>
   </si>
@@ -561,10 +561,10 @@
     <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
@@ -4694,10 +4694,33 @@
       </c>
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F148" s="2"/>
-      <c r="G148" s="1"/>
-      <c r="H148" s="2"/>
-      <c r="I148" s="1"/>
+      <c r="B148" t="s">
+        <v>40</v>
+      </c>
+      <c r="C148">
+        <v>676</v>
+      </c>
+      <c r="D148" t="s">
+        <v>44</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H148" s="2">
+        <v>7.4305555555555557E-3</v>
+      </c>
+      <c r="I148" s="1">
+        <v>46176.425347222219</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F149" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685EDF14-735D-4E12-B3E4-05CE29297531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DDE790-03E5-4646-9FDA-9D0A51C0B38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="345" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="47">
   <si>
     <t>Company Name</t>
   </si>
@@ -621,7 +621,7 @@
       <c r="I2" s="1">
         <v>45428.49114583333</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" t="s">
@@ -650,7 +650,7 @@
       <c r="I3" s="1">
         <v>45428.49114583333</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>0</v>
       </c>
       <c r="K3" t="s">
@@ -679,7 +679,7 @@
       <c r="I4" s="1">
         <v>45428.49114583333</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" t="s">
@@ -708,7 +708,7 @@
       <c r="I5" s="1">
         <v>45428.49114583333</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" t="s">
@@ -737,7 +737,7 @@
       <c r="I6" s="1">
         <v>45428.49114583333</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" t="s">
@@ -766,7 +766,7 @@
       <c r="I7" s="1">
         <v>45446.590231481481</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>2</v>
       </c>
       <c r="K7" t="s">
@@ -795,7 +795,7 @@
       <c r="I8" s="1">
         <v>45446.590231481481</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>2</v>
       </c>
       <c r="K8" t="s">
@@ -824,7 +824,7 @@
       <c r="I9" s="1">
         <v>45446.590231481481</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="K9" t="s">
@@ -853,7 +853,7 @@
       <c r="I10" s="1">
         <v>45446.590231481481</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" t="s">
@@ -882,7 +882,7 @@
       <c r="I11" s="1">
         <v>45446.590231481481</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>1</v>
       </c>
       <c r="K11" t="s">
@@ -911,7 +911,7 @@
       <c r="I12" s="1">
         <v>45474.73642361111</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>2</v>
       </c>
       <c r="K12" t="s">
@@ -940,7 +940,7 @@
       <c r="I13" s="1">
         <v>45474.73642361111</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>0</v>
       </c>
       <c r="K13" t="s">
@@ -969,7 +969,7 @@
       <c r="I14" s="1">
         <v>45474.73642361111</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14" t="s">
@@ -998,7 +998,7 @@
       <c r="I15" s="1">
         <v>45474.73642361111</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" t="s">
@@ -1027,7 +1027,7 @@
       <c r="I16" s="1">
         <v>45474.73642361111</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>1</v>
       </c>
       <c r="K16" t="s">
@@ -1056,7 +1056,7 @@
       <c r="I17" s="1">
         <v>45509.521689814814</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" t="s">
@@ -1094,7 +1094,7 @@
       <c r="I19" s="1">
         <v>45509.521689814814</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" t="s">
@@ -1123,7 +1123,7 @@
       <c r="I20" s="1">
         <v>45509.521689814814</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" t="s">
@@ -1152,7 +1152,7 @@
       <c r="I21" s="1">
         <v>45509.521689814814</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>0</v>
       </c>
       <c r="K21" t="s">
@@ -1181,7 +1181,7 @@
       <c r="I22" s="1">
         <v>45509.521689814814</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>0</v>
       </c>
       <c r="K22" t="s">
@@ -1210,7 +1210,7 @@
       <c r="I23" s="1">
         <v>45517.482627314814</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>0</v>
       </c>
       <c r="K23" t="s">
@@ -1239,7 +1239,7 @@
       <c r="I24" s="1">
         <v>45523.511666666665</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>0</v>
       </c>
       <c r="K24" t="s">
@@ -1268,7 +1268,7 @@
       <c r="I25" s="1">
         <v>45523.511666666665</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>1</v>
       </c>
       <c r="K25" t="s">
@@ -1297,7 +1297,7 @@
       <c r="I26" s="1">
         <v>45523.511666666665</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>0</v>
       </c>
       <c r="K26" t="s">
@@ -1326,7 +1326,7 @@
       <c r="I27" s="1">
         <v>45538.766932870371</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>0</v>
       </c>
       <c r="K27" t="s">
@@ -1355,7 +1355,7 @@
       <c r="I28" s="1">
         <v>45538.766932870371</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>0</v>
       </c>
       <c r="K28" t="s">
@@ -1384,7 +1384,7 @@
       <c r="I29" s="1">
         <v>45538.766932870371</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>0</v>
       </c>
       <c r="K29" t="s">
@@ -1413,7 +1413,7 @@
       <c r="I30" s="1">
         <v>45538.766932870371</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>2</v>
       </c>
       <c r="K30" t="s">
@@ -1442,7 +1442,7 @@
       <c r="I31" s="1">
         <v>45538.766932870371</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>0</v>
       </c>
       <c r="K31" t="s">
@@ -1471,7 +1471,7 @@
       <c r="I32" s="1">
         <v>45538.766932870371</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>0</v>
       </c>
       <c r="K32" t="s">
@@ -1500,7 +1500,7 @@
       <c r="I33" s="1">
         <v>45572.748055555552</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
         <v>0</v>
       </c>
       <c r="K33" t="s">
@@ -1529,7 +1529,7 @@
       <c r="I34" s="1">
         <v>45572.748055555552</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>0</v>
       </c>
       <c r="K34" t="s">
@@ -1558,7 +1558,7 @@
       <c r="I35" s="1">
         <v>45572.748055555552</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
         <v>0</v>
       </c>
       <c r="K35" t="s">
@@ -1587,7 +1587,7 @@
       <c r="I36" s="1">
         <v>45572.748055555552</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="1">
         <v>3</v>
       </c>
       <c r="K36" t="s">
@@ -1616,7 +1616,7 @@
       <c r="I37" s="1">
         <v>45572.748055555552</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="1">
         <v>1</v>
       </c>
       <c r="K37" t="s">
@@ -1645,7 +1645,7 @@
       <c r="I38" s="1">
         <v>45572.748055555552</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
         <v>3</v>
       </c>
       <c r="K38" t="s">
@@ -1674,7 +1674,7 @@
       <c r="I39" s="1">
         <v>45600.862893518519</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
         <v>2</v>
       </c>
       <c r="K39" t="s">
@@ -1703,7 +1703,7 @@
       <c r="I40" s="1">
         <v>45600.862893518519</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="1">
         <v>1</v>
       </c>
       <c r="K40" t="s">
@@ -1732,7 +1732,7 @@
       <c r="I41" s="1">
         <v>45600.862893518519</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="1">
         <v>0</v>
       </c>
       <c r="K41" t="s">
@@ -1761,7 +1761,7 @@
       <c r="I42" s="1">
         <v>45600.862893518519</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="1">
         <v>1</v>
       </c>
       <c r="K42" t="s">
@@ -1790,7 +1790,7 @@
       <c r="I43" s="1">
         <v>45600.862893518519</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="1">
         <v>0</v>
       </c>
       <c r="K43" t="s">
@@ -1819,7 +1819,7 @@
       <c r="I44" s="1">
         <v>45600.862893518519</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="1">
         <v>0</v>
       </c>
       <c r="K44" t="s">
@@ -1848,7 +1848,7 @@
       <c r="I45" s="1">
         <v>45629.707789351851</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="1">
         <v>0</v>
       </c>
       <c r="K45" t="s">
@@ -1877,7 +1877,7 @@
       <c r="I46" s="1">
         <v>45629.707789351851</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="1">
         <v>0</v>
       </c>
       <c r="K46" t="s">
@@ -1906,7 +1906,7 @@
       <c r="I47" s="1">
         <v>45629.707789351851</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="1">
         <v>1</v>
       </c>
       <c r="K47" t="s">
@@ -1935,7 +1935,7 @@
       <c r="I48" s="1">
         <v>45629.707789351851</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="1">
         <v>3</v>
       </c>
       <c r="K48" t="s">
@@ -1964,7 +1964,7 @@
       <c r="I49" s="1">
         <v>45629.707789351851</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="1">
         <v>0</v>
       </c>
       <c r="K49" t="s">
@@ -1993,7 +1993,7 @@
       <c r="I50" s="1">
         <v>45629.707789351851</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="1">
         <v>0</v>
       </c>
       <c r="K50" t="s">
@@ -2022,7 +2022,7 @@
       <c r="I51" s="1">
         <v>45663.551157407404</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="1">
         <v>2</v>
       </c>
       <c r="K51" t="s">
@@ -2051,7 +2051,7 @@
       <c r="I52" s="1">
         <v>45663.551851851851</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="1">
         <v>0</v>
       </c>
       <c r="K52" t="s">
@@ -2080,7 +2080,7 @@
       <c r="I53" s="1">
         <v>45663.551851851851</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="1">
         <v>1</v>
       </c>
       <c r="K53" t="s">
@@ -2109,7 +2109,7 @@
       <c r="I54" s="1">
         <v>45663.551851851851</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="1">
         <v>1</v>
       </c>
       <c r="K54" t="s">
@@ -2138,7 +2138,7 @@
       <c r="I55" s="1">
         <v>45663.552546296298</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="1">
         <v>0</v>
       </c>
       <c r="K55" t="s">
@@ -2167,7 +2167,7 @@
       <c r="I56" s="1">
         <v>45663.552546296298</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="1">
         <v>0</v>
       </c>
       <c r="K56" t="s">
@@ -2196,7 +2196,7 @@
       <c r="I57" s="1">
         <v>45691.794675925928</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="1">
         <v>3</v>
       </c>
       <c r="K57" t="s">
@@ -2234,7 +2234,7 @@
       <c r="I59" s="1">
         <v>45691.795370370368</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="1">
         <v>3</v>
       </c>
       <c r="K59" t="s">
@@ -2263,7 +2263,7 @@
       <c r="I60" s="1">
         <v>45691.796064814815</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="1">
         <v>0</v>
       </c>
       <c r="K60" t="s">
@@ -2292,7 +2292,7 @@
       <c r="I61" s="1">
         <v>45691.796064814815</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="1">
         <v>3</v>
       </c>
       <c r="K61" t="s">
@@ -2321,7 +2321,7 @@
       <c r="I62" s="1">
         <v>45691.796759259261</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="1">
         <v>0</v>
       </c>
       <c r="K62" t="s">
@@ -2350,7 +2350,7 @@
       <c r="I63" s="1">
         <v>45691.796759259261</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="1">
         <v>2</v>
       </c>
       <c r="K63" t="s">
@@ -2379,7 +2379,7 @@
       <c r="I64" s="1">
         <v>45719.806597222225</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="1">
         <v>2</v>
       </c>
       <c r="K64" t="s">
@@ -2408,7 +2408,7 @@
       <c r="I65" s="1">
         <v>45719.807291666664</v>
       </c>
-      <c r="J65">
+      <c r="J65" s="1">
         <v>2</v>
       </c>
       <c r="K65" t="s">
@@ -2437,7 +2437,7 @@
       <c r="I66" s="1">
         <v>45719.807291666664</v>
       </c>
-      <c r="J66">
+      <c r="J66" s="1">
         <v>0</v>
       </c>
       <c r="K66" t="s">
@@ -2466,7 +2466,7 @@
       <c r="I67" s="1">
         <v>45719.807986111111</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="1">
         <v>1</v>
       </c>
       <c r="K67" t="s">
@@ -2495,7 +2495,7 @@
       <c r="I68" s="1">
         <v>45719.808680555558</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="1">
         <v>0</v>
       </c>
       <c r="K68" t="s">
@@ -2524,7 +2524,7 @@
       <c r="I69" s="1">
         <v>45719.808680555558</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="1">
         <v>2</v>
       </c>
       <c r="K69" t="s">
@@ -2553,7 +2553,7 @@
       <c r="I70" s="1">
         <v>45754.931481481479</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="1">
         <v>2</v>
       </c>
       <c r="K70" t="s">
@@ -2582,7 +2582,7 @@
       <c r="I71" s="1">
         <v>45754.932175925926</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="1">
         <v>2</v>
       </c>
       <c r="K71" t="s">
@@ -2611,7 +2611,7 @@
       <c r="I72" s="1">
         <v>45754.932175925926</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="1">
         <v>0</v>
       </c>
       <c r="K72" t="s">
@@ -2640,7 +2640,7 @@
       <c r="I73" s="1">
         <v>45754.932870370372</v>
       </c>
-      <c r="J73">
+      <c r="J73" s="1">
         <v>2</v>
       </c>
       <c r="K73" t="s">
@@ -2669,7 +2669,7 @@
       <c r="I74" s="1">
         <v>45754.932870370372</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="1">
         <v>0</v>
       </c>
       <c r="K74" t="s">
@@ -2698,7 +2698,7 @@
       <c r="I75" s="1">
         <v>45754.933564814812</v>
       </c>
-      <c r="J75">
+      <c r="J75" s="1">
         <v>1</v>
       </c>
       <c r="K75" t="s">
@@ -2727,7 +2727,7 @@
       <c r="I76" s="1">
         <v>45782.804976851854</v>
       </c>
-      <c r="J76">
+      <c r="J76" s="1">
         <v>3</v>
       </c>
       <c r="K76" t="s">
@@ -2756,7 +2756,7 @@
       <c r="I77" s="1">
         <v>45782.804976851854</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="1">
         <v>0</v>
       </c>
       <c r="K77" t="s">
@@ -2785,7 +2785,7 @@
       <c r="I78" s="1">
         <v>45782.805671296293</v>
       </c>
-      <c r="J78">
+      <c r="J78" s="1">
         <v>0</v>
       </c>
       <c r="K78" t="s">
@@ -2814,7 +2814,7 @@
       <c r="I79" s="1">
         <v>45782.805671296293</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="1">
         <v>3</v>
       </c>
       <c r="K79" t="s">
@@ -2843,7 +2843,7 @@
       <c r="I80" s="1">
         <v>45782.80636574074</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="1">
         <v>0</v>
       </c>
       <c r="K80" t="s">
@@ -2872,7 +2872,7 @@
       <c r="I81" s="1">
         <v>45782.80636574074</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="1">
         <v>0</v>
       </c>
       <c r="K81" t="s">
@@ -2901,7 +2901,7 @@
       <c r="I82" s="1">
         <v>45810.803124999999</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="1">
         <v>0</v>
       </c>
       <c r="K82" t="s">
@@ -2930,7 +2930,7 @@
       <c r="I83" s="1">
         <v>45810.803124999999</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="1">
         <v>0</v>
       </c>
       <c r="K83" t="s">
@@ -2959,7 +2959,7 @@
       <c r="I84" s="1">
         <v>45810.803819444445</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="1">
         <v>0</v>
       </c>
       <c r="K84" t="s">
@@ -2988,7 +2988,7 @@
       <c r="I85" s="1">
         <v>45810.804513888892</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="1">
         <v>1</v>
       </c>
       <c r="K85" t="s">
@@ -3017,7 +3017,7 @@
       <c r="I86" s="1">
         <v>45810.804513888892</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="1">
         <v>0</v>
       </c>
       <c r="K86" t="s">
@@ -3046,7 +3046,7 @@
       <c r="I87" s="1">
         <v>45810.805208333331</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="1">
         <v>1</v>
       </c>
       <c r="K87" t="s">
@@ -3075,7 +3075,7 @@
       <c r="I88" s="1">
         <v>45845.557986111111</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="1">
         <v>1</v>
       </c>
       <c r="K88" t="s">
@@ -3104,7 +3104,7 @@
       <c r="I89" s="1">
         <v>45845.54351851852</v>
       </c>
-      <c r="J89">
+      <c r="J89" s="1">
         <v>1</v>
       </c>
       <c r="K89" t="s">
@@ -3133,7 +3133,7 @@
       <c r="I90" s="1">
         <v>45845.544212962966</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="1">
         <v>0</v>
       </c>
       <c r="K90" t="s">
@@ -3162,7 +3162,7 @@
       <c r="I91" s="1">
         <v>45845.544212962966</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="1">
         <v>1</v>
       </c>
       <c r="K91" t="s">
@@ -3191,7 +3191,7 @@
       <c r="I92" s="1">
         <v>45845.544907407406</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="1">
         <v>0</v>
       </c>
       <c r="K92" t="s">
@@ -3220,7 +3220,7 @@
       <c r="I93" s="1">
         <v>45845.544907407406</v>
       </c>
-      <c r="J93">
+      <c r="J93" s="1">
         <v>1</v>
       </c>
       <c r="K93" t="s">
@@ -3249,7 +3249,7 @@
       <c r="I94" s="1">
         <v>45873.632060185184</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="1">
         <v>3</v>
       </c>
       <c r="K94" t="s">
@@ -3278,7 +3278,7 @@
       <c r="I95" s="1">
         <v>45873.632754629631</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="1">
         <v>0</v>
       </c>
       <c r="K95" t="s">
@@ -3307,7 +3307,7 @@
       <c r="I96" s="1">
         <v>45873.632754629631</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="1">
         <v>1</v>
       </c>
       <c r="K96" t="s">
@@ -3336,7 +3336,7 @@
       <c r="I97" s="1">
         <v>45873.633449074077</v>
       </c>
-      <c r="J97">
+      <c r="J97" s="1">
         <v>3</v>
       </c>
       <c r="K97" t="s">
@@ -3365,7 +3365,7 @@
       <c r="I98" s="1">
         <v>45873.633449074077</v>
       </c>
-      <c r="J98">
+      <c r="J98" s="1">
         <v>0</v>
       </c>
       <c r="K98" t="s">
@@ -3394,7 +3394,7 @@
       <c r="I99" s="1">
         <v>45873.633449074077</v>
       </c>
-      <c r="J99">
+      <c r="J99" s="1">
         <v>0</v>
       </c>
       <c r="K99" t="s">
@@ -3423,7 +3423,7 @@
       <c r="I100" s="1">
         <v>45902.088425925926</v>
       </c>
-      <c r="J100">
+      <c r="J100" s="1">
         <v>2</v>
       </c>
       <c r="K100" t="s">
@@ -3452,7 +3452,7 @@
       <c r="I101" s="1">
         <v>45902.088425925926</v>
       </c>
-      <c r="J101">
+      <c r="J101" s="1">
         <v>0</v>
       </c>
       <c r="K101" t="s">
@@ -3481,7 +3481,7 @@
       <c r="I102" s="1">
         <v>45902.089120370372</v>
       </c>
-      <c r="J102">
+      <c r="J102" s="1">
         <v>0</v>
       </c>
       <c r="K102" t="s">
@@ -3510,7 +3510,7 @@
       <c r="I103" s="1">
         <v>45902.089120370372</v>
       </c>
-      <c r="J103">
+      <c r="J103" s="1">
         <v>2</v>
       </c>
       <c r="K103" t="s">
@@ -3539,7 +3539,7 @@
       <c r="I104" s="1">
         <v>45902.089814814812</v>
       </c>
-      <c r="J104">
+      <c r="J104" s="1">
         <v>0</v>
       </c>
       <c r="K104" t="s">
@@ -3568,7 +3568,7 @@
       <c r="I105" s="1">
         <v>45902.089814814812</v>
       </c>
-      <c r="J105">
+      <c r="J105" s="1">
         <v>2</v>
       </c>
       <c r="K105" t="s">
@@ -3597,7 +3597,7 @@
       <c r="I106" s="1">
         <v>45936.849537037036</v>
       </c>
-      <c r="J106">
+      <c r="J106" s="1">
         <v>5</v>
       </c>
       <c r="K106" t="s">
@@ -3626,7 +3626,7 @@
       <c r="I107" s="1">
         <v>45936.849537037036</v>
       </c>
-      <c r="J107">
+      <c r="J107" s="1">
         <v>1</v>
       </c>
       <c r="K107" t="s">
@@ -3655,7 +3655,7 @@
       <c r="I108" s="1">
         <v>45936.850231481483</v>
       </c>
-      <c r="J108">
+      <c r="J108" s="1">
         <v>0</v>
       </c>
       <c r="K108" t="s">
@@ -3684,7 +3684,7 @@
       <c r="I109" s="1">
         <v>45936.850231481483</v>
       </c>
-      <c r="J109">
+      <c r="J109" s="1">
         <v>5</v>
       </c>
       <c r="K109" t="s">
@@ -3713,7 +3713,7 @@
       <c r="I110" s="1">
         <v>45936.850925925923</v>
       </c>
-      <c r="J110">
+      <c r="J110" s="1">
         <v>0</v>
       </c>
       <c r="K110" t="s">
@@ -3742,7 +3742,7 @@
       <c r="I111" s="1">
         <v>45936.850925925923</v>
       </c>
-      <c r="J111">
+      <c r="J111" s="1">
         <v>2</v>
       </c>
       <c r="K111" t="s">
@@ -3771,7 +3771,7 @@
       <c r="I112" s="1">
         <v>45964.886111111111</v>
       </c>
-      <c r="J112">
+      <c r="J112" s="1">
         <v>4</v>
       </c>
       <c r="K112" t="s">
@@ -3800,7 +3800,7 @@
       <c r="I113" s="1">
         <v>45964.886111111111</v>
       </c>
-      <c r="J113">
+      <c r="J113" s="1">
         <v>0</v>
       </c>
       <c r="K113" t="s">
@@ -3829,7 +3829,7 @@
       <c r="I114" s="1">
         <v>45964.886805555558</v>
       </c>
-      <c r="J114">
+      <c r="J114" s="1">
         <v>2</v>
       </c>
       <c r="K114" t="s">
@@ -3858,7 +3858,7 @@
       <c r="I115" s="1">
         <v>45964.887499999997</v>
       </c>
-      <c r="J115">
+      <c r="J115" s="1">
         <v>4</v>
       </c>
       <c r="K115" t="s">
@@ -3887,7 +3887,7 @@
       <c r="I116" s="1">
         <v>45964.888194444444</v>
       </c>
-      <c r="J116">
+      <c r="J116" s="1">
         <v>2</v>
       </c>
       <c r="K116" t="s">
@@ -3916,7 +3916,7 @@
       <c r="I117" s="1">
         <v>45964.888194444444</v>
       </c>
-      <c r="J117">
+      <c r="J117" s="1">
         <v>2</v>
       </c>
       <c r="K117" t="s">
@@ -3954,7 +3954,7 @@
       <c r="I119" s="1">
         <v>45992.680208333331</v>
       </c>
-      <c r="J119">
+      <c r="J119" s="1">
         <v>3</v>
       </c>
       <c r="K119" t="s">
@@ -3983,7 +3983,7 @@
       <c r="I120" s="1">
         <v>45992.680208333331</v>
       </c>
-      <c r="J120">
+      <c r="J120" s="1">
         <v>2</v>
       </c>
       <c r="K120" t="s">
@@ -4012,7 +4012,7 @@
       <c r="I121" s="1">
         <v>45992.680902777778</v>
       </c>
-      <c r="J121">
+      <c r="J121" s="1">
         <v>0</v>
       </c>
       <c r="K121" t="s">
@@ -4041,7 +4041,7 @@
       <c r="I122" s="1">
         <v>45992.680902777778</v>
       </c>
-      <c r="J122">
+      <c r="J122" s="1">
         <v>1</v>
       </c>
       <c r="K122" t="s">
@@ -4070,7 +4070,7 @@
       <c r="I123" s="1">
         <v>46028.754745370374</v>
       </c>
-      <c r="J123">
+      <c r="J123" s="1">
         <v>0</v>
       </c>
       <c r="K123" t="s">
@@ -4099,7 +4099,7 @@
       <c r="I124" s="1">
         <v>46028.754745370374</v>
       </c>
-      <c r="J124">
+      <c r="J124" s="1">
         <v>1</v>
       </c>
       <c r="K124" t="s">
@@ -4128,7 +4128,7 @@
       <c r="I125" s="1">
         <v>46028.755439814813</v>
       </c>
-      <c r="J125">
+      <c r="J125" s="1">
         <v>2</v>
       </c>
       <c r="K125" t="s">
@@ -4157,7 +4157,7 @@
       <c r="I126" s="1">
         <v>46028.75613425926</v>
       </c>
-      <c r="J126">
+      <c r="J126" s="1">
         <v>3</v>
       </c>
       <c r="K126" t="s">
@@ -4195,7 +4195,7 @@
       <c r="I128" s="1">
         <v>46055.898842592593</v>
       </c>
-      <c r="J128">
+      <c r="J128" s="1">
         <v>5</v>
       </c>
       <c r="K128" t="s">
@@ -4224,7 +4224,7 @@
       <c r="I129" s="1">
         <v>46055.899537037039</v>
       </c>
-      <c r="J129">
+      <c r="J129" s="1">
         <v>4</v>
       </c>
       <c r="K129" t="s">
@@ -4253,7 +4253,7 @@
       <c r="I130" s="1">
         <v>46055.900231481479</v>
       </c>
-      <c r="J130">
+      <c r="J130" s="1">
         <v>0</v>
       </c>
       <c r="K130" t="s">
@@ -4282,7 +4282,7 @@
       <c r="I131" s="1">
         <v>46055.900231481479</v>
       </c>
-      <c r="J131">
+      <c r="J131" s="1">
         <v>0</v>
       </c>
       <c r="K131" t="s">
@@ -4320,7 +4320,7 @@
       <c r="I133" s="1">
         <v>46083.81354166667</v>
       </c>
-      <c r="J133">
+      <c r="J133" s="1">
         <v>3</v>
       </c>
       <c r="K133" t="s">
@@ -4349,7 +4349,7 @@
       <c r="I134" s="1">
         <v>46083.814236111109</v>
       </c>
-      <c r="J134">
+      <c r="J134" s="1">
         <v>0</v>
       </c>
       <c r="K134" t="s">
@@ -4378,7 +4378,7 @@
       <c r="I135" s="1">
         <v>46083.814236111109</v>
       </c>
-      <c r="J135">
+      <c r="J135" s="1">
         <v>0</v>
       </c>
       <c r="K135" t="s">
@@ -4407,7 +4407,7 @@
       <c r="I136" s="1">
         <v>46083.814930555556</v>
       </c>
-      <c r="J136">
+      <c r="J136" s="1">
         <v>0</v>
       </c>
       <c r="K136" t="s">
@@ -4436,7 +4436,7 @@
       <c r="I137" s="1">
         <v>46118.810995370368</v>
       </c>
-      <c r="J137">
+      <c r="J137" s="1">
         <v>4</v>
       </c>
       <c r="K137" t="s">
@@ -4465,7 +4465,7 @@
       <c r="I138" s="1">
         <v>46118.811689814815</v>
       </c>
-      <c r="J138">
+      <c r="J138" s="1">
         <v>3</v>
       </c>
       <c r="K138" t="s">
@@ -4494,7 +4494,7 @@
       <c r="I139" s="1">
         <v>46118.811689814815</v>
       </c>
-      <c r="J139">
+      <c r="J139" s="1">
         <v>1</v>
       </c>
       <c r="K139" t="s">
@@ -4532,7 +4532,7 @@
       <c r="I141" s="1">
         <v>46118.812384259261</v>
       </c>
-      <c r="J141">
+      <c r="J141" s="1">
         <v>1</v>
       </c>
       <c r="K141" t="s">
@@ -4570,7 +4570,7 @@
       <c r="I143" s="1">
         <v>46146.728819444441</v>
       </c>
-      <c r="J143">
+      <c r="J143" s="1">
         <v>2</v>
       </c>
       <c r="K143" t="s">
@@ -4599,7 +4599,7 @@
       <c r="I144" s="1">
         <v>46146.729513888888</v>
       </c>
-      <c r="J144">
+      <c r="J144" s="1">
         <v>0</v>
       </c>
       <c r="K144" t="s">
@@ -4628,7 +4628,7 @@
       <c r="I145" s="1">
         <v>46146.729513888888</v>
       </c>
-      <c r="J145">
+      <c r="J145" s="1">
         <v>3</v>
       </c>
       <c r="K145" t="s">
@@ -4657,7 +4657,7 @@
       <c r="I146" s="1">
         <v>46176.425347222219</v>
       </c>
-      <c r="J146">
+      <c r="J146" s="1">
         <v>0</v>
       </c>
       <c r="K146" t="s">
@@ -4686,7 +4686,7 @@
       <c r="I147" s="1">
         <v>46176.425347222219</v>
       </c>
-      <c r="J147">
+      <c r="J147" s="1">
         <v>0</v>
       </c>
       <c r="K147" t="s">
@@ -4694,33 +4694,10 @@
       </c>
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>40</v>
-      </c>
-      <c r="C148">
-        <v>676</v>
-      </c>
-      <c r="D148" t="s">
-        <v>44</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H148" s="2">
-        <v>7.4305555555555557E-3</v>
-      </c>
-      <c r="I148" s="1">
-        <v>46176.425347222219</v>
-      </c>
-      <c r="J148">
-        <v>1</v>
-      </c>
-      <c r="K148" t="s">
-        <v>11</v>
-      </c>
+      <c r="F148" s="2"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="1"/>
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F149" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6741C66F-DDD8-4A2B-8101-EB888E53E8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE670781-5C46-4273-83A9-0FF7A453CDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="47">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,6 +86,9 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -95,10 +98,19 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -110,13 +122,7 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Safe Lifting for Commercial Drivers</t>
-  </si>
-  <si>
     <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>DNU-Scene of an Accident</t>
@@ -125,40 +131,28 @@
     <t>DNU-NEW-Vehicle Inspections</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
   </si>
   <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Micro-Learn Space Mangement</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
-  </si>
-  <si>
-    <t>Backing Commercial Vehicles</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>The Electric Light &amp; Power Company</t>
@@ -180,6 +174,12 @@
   </si>
   <si>
     <t>Alex Kleck</t>
+  </si>
+  <si>
+    <t>Backing Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Micro-Learn Space Mangement</t>
   </si>
 </sst>
 </file>
@@ -553,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -602,16 +602,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>678</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -631,16 +631,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>680</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -660,16 +660,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>677</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -689,16 +689,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>676</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -718,16 +718,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>679</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -747,16 +747,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -776,16 +776,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>680</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -805,16 +805,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>677</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -834,16 +834,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>676</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -863,16 +863,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>679</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -892,16 +892,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>678</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -921,16 +921,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>680</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -950,16 +950,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>677</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -979,16 +979,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>676</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1008,16 +1008,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E16">
         <v>679</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1037,16 +1037,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>678</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>12</v>
@@ -1070,21 +1070,21 @@
       <c r="J18" s="2"/>
       <c r="K18" s="1"/>
       <c r="M18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>680</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1104,16 +1104,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>677</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1133,16 +1133,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>676</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1162,16 +1162,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>679</v>
       </c>
       <c r="F22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1191,16 +1191,16 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23">
         <v>2168</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1220,16 +1220,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24">
         <v>2168</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1249,16 +1249,16 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E25">
         <v>678</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E26">
         <v>679</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27">
         <v>2168</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1336,16 +1336,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E28">
         <v>678</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1365,16 +1365,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>680</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E30">
         <v>677</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1423,16 +1423,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>676</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1452,16 +1452,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32">
         <v>679</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1481,16 +1481,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>2168</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1510,16 +1510,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E34">
         <v>678</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1539,16 +1539,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E35">
         <v>680</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1568,16 +1568,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E36">
         <v>677</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E37">
         <v>676</v>
       </c>
       <c r="F37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1626,16 +1626,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E38">
         <v>679</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1655,16 +1655,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E39">
         <v>2168</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1684,16 +1684,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E40">
         <v>678</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E41">
         <v>680</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1742,16 +1742,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E42">
         <v>677</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1771,16 +1771,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E43">
         <v>676</v>
       </c>
       <c r="F43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1800,16 +1800,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E44">
         <v>679</v>
       </c>
       <c r="F44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1829,16 +1829,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E45">
         <v>2168</v>
       </c>
       <c r="F45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1858,16 +1858,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E46">
         <v>678</v>
       </c>
       <c r="F46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1887,16 +1887,16 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E47">
         <v>680</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1916,16 +1916,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E48">
         <v>677</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1945,16 +1945,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E49">
         <v>676</v>
       </c>
       <c r="F49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E50">
         <v>679</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2003,16 +2003,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E51">
         <v>2168</v>
       </c>
       <c r="F51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E52">
         <v>678</v>
       </c>
       <c r="F52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2061,16 +2061,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E53">
         <v>680</v>
       </c>
       <c r="F53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -2090,16 +2090,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E54">
         <v>677</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2119,16 +2119,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E55">
         <v>676</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2148,16 +2148,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E56">
         <v>679</v>
       </c>
       <c r="F56" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2177,16 +2177,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E57">
         <v>2168</v>
       </c>
       <c r="F57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>12</v>
@@ -2210,21 +2210,21 @@
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
       <c r="M58" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E59">
         <v>678</v>
       </c>
       <c r="F59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2244,16 +2244,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E60">
         <v>680</v>
       </c>
       <c r="F60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2273,16 +2273,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E61">
         <v>677</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2302,16 +2302,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E62">
         <v>676</v>
       </c>
       <c r="F62" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2331,16 +2331,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E63">
         <v>679</v>
       </c>
       <c r="F63" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2360,16 +2360,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E64">
         <v>2168</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2389,16 +2389,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E65">
         <v>678</v>
       </c>
       <c r="F65" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2418,16 +2418,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E66">
         <v>680</v>
       </c>
       <c r="F66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2447,16 +2447,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E67">
         <v>677</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2476,16 +2476,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E68">
         <v>676</v>
       </c>
       <c r="F68" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2505,16 +2505,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E69">
         <v>679</v>
       </c>
       <c r="F69" t="s">
+        <v>43</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E70">
         <v>2168</v>
       </c>
       <c r="F70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2563,16 +2563,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E71">
         <v>678</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2592,16 +2592,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E72">
         <v>680</v>
       </c>
       <c r="F72" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2621,16 +2621,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E73">
         <v>677</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2650,16 +2650,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E74">
         <v>676</v>
       </c>
       <c r="F74" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E75">
         <v>679</v>
       </c>
       <c r="F75" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2708,16 +2708,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E76">
         <v>2168</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2737,16 +2737,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E77">
         <v>678</v>
       </c>
       <c r="F77" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2766,16 +2766,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E78">
         <v>680</v>
       </c>
       <c r="F78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2795,16 +2795,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E79">
         <v>677</v>
       </c>
       <c r="F79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2824,16 +2824,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E80">
         <v>676</v>
       </c>
       <c r="F80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2853,16 +2853,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E81">
         <v>679</v>
       </c>
       <c r="F81" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2882,16 +2882,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E82">
         <v>2168</v>
       </c>
       <c r="F82" t="s">
+        <v>44</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2911,16 +2911,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E83">
         <v>678</v>
       </c>
       <c r="F83" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2940,16 +2940,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E84">
         <v>680</v>
       </c>
       <c r="F84" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2969,16 +2969,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E85">
         <v>677</v>
       </c>
       <c r="F85" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E86">
         <v>676</v>
       </c>
       <c r="F86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -3027,16 +3027,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E87">
         <v>679</v>
       </c>
       <c r="F87" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3056,16 +3056,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E88">
         <v>2168</v>
       </c>
       <c r="F88" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3085,16 +3085,16 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E89">
         <v>678</v>
       </c>
       <c r="F89" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E90">
         <v>680</v>
       </c>
       <c r="F90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3143,16 +3143,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E91">
         <v>677</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3172,16 +3172,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E92">
         <v>676</v>
       </c>
       <c r="F92" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3201,16 +3201,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E93">
         <v>679</v>
       </c>
       <c r="F93" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3230,16 +3230,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E94">
         <v>2168</v>
       </c>
       <c r="F94" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3259,16 +3259,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E95">
         <v>678</v>
       </c>
       <c r="F95" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3288,16 +3288,16 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E96">
         <v>680</v>
       </c>
       <c r="F96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3317,16 +3317,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E97">
         <v>677</v>
       </c>
       <c r="F97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3346,16 +3346,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E98">
         <v>676</v>
       </c>
       <c r="F98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3375,16 +3375,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E99">
         <v>679</v>
       </c>
       <c r="F99" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3404,16 +3404,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E100">
         <v>2168</v>
       </c>
       <c r="F100" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3433,16 +3433,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E101">
         <v>678</v>
       </c>
       <c r="F101" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E102">
         <v>680</v>
       </c>
       <c r="F102" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3491,16 +3491,16 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E103">
         <v>677</v>
       </c>
       <c r="F103" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3520,16 +3520,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E104">
         <v>676</v>
       </c>
       <c r="F104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3549,16 +3549,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E105">
         <v>679</v>
       </c>
       <c r="F105" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3578,16 +3578,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E106">
         <v>2168</v>
       </c>
       <c r="F106" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3607,16 +3607,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E107">
         <v>678</v>
       </c>
       <c r="F107" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3636,16 +3636,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E108">
         <v>680</v>
       </c>
       <c r="F108" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3665,16 +3665,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E109">
         <v>677</v>
       </c>
       <c r="F109" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E110">
         <v>676</v>
       </c>
       <c r="F110" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3723,16 +3723,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E111">
         <v>679</v>
       </c>
       <c r="F111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3752,16 +3752,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E112">
         <v>2168</v>
       </c>
       <c r="F112" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3781,16 +3781,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E113">
         <v>678</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3810,16 +3810,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E114">
         <v>680</v>
       </c>
       <c r="F114" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -3839,16 +3839,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E115">
         <v>677</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3868,16 +3868,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E116">
         <v>676</v>
       </c>
       <c r="F116" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3897,16 +3897,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E117">
         <v>679</v>
       </c>
       <c r="F117" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>12</v>
@@ -3930,21 +3930,21 @@
       <c r="J118" s="2"/>
       <c r="K118" s="1"/>
       <c r="M118" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E119">
         <v>678</v>
       </c>
       <c r="F119" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3964,16 +3964,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E120">
         <v>680</v>
       </c>
       <c r="F120" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3993,16 +3993,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E121">
         <v>676</v>
       </c>
       <c r="F121" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -4022,16 +4022,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E122">
         <v>679</v>
       </c>
       <c r="F122" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -4051,16 +4051,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E123">
         <v>678</v>
       </c>
       <c r="F123" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4080,16 +4080,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E124">
         <v>680</v>
       </c>
       <c r="F124" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4109,16 +4109,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E125">
         <v>676</v>
       </c>
       <c r="F125" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4138,16 +4138,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E126">
         <v>679</v>
       </c>
       <c r="F126" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>14</v>
@@ -4171,21 +4171,21 @@
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
       <c r="M127" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E128">
         <v>678</v>
       </c>
       <c r="F128" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>10</v>
@@ -4205,16 +4205,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E129">
         <v>680</v>
       </c>
       <c r="F129" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4234,16 +4234,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E130">
         <v>676</v>
       </c>
       <c r="F130" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4263,16 +4263,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E131">
         <v>679</v>
       </c>
       <c r="F131" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>14</v>
@@ -4296,21 +4296,21 @@
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
       <c r="M132" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E133">
         <v>678</v>
       </c>
       <c r="F133" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4330,16 +4330,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E134">
         <v>680</v>
       </c>
       <c r="F134" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4359,16 +4359,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E135">
         <v>676</v>
       </c>
       <c r="F135" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4388,16 +4388,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E136">
         <v>679</v>
       </c>
       <c r="F136" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4417,16 +4417,16 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E137">
         <v>678</v>
       </c>
       <c r="F137" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4446,16 +4446,16 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E138">
         <v>680</v>
       </c>
       <c r="F138" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4475,16 +4475,16 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E139">
         <v>676</v>
       </c>
       <c r="F139" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>12</v>
@@ -4508,21 +4508,21 @@
       <c r="J140" s="2"/>
       <c r="K140" s="1"/>
       <c r="M140" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E141">
         <v>679</v>
       </c>
       <c r="F141" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>12</v>
@@ -4546,21 +4546,21 @@
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
       <c r="M142" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E143">
         <v>678</v>
       </c>
       <c r="F143" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4580,16 +4580,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E144">
         <v>680</v>
       </c>
       <c r="F144" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4609,16 +4609,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E145">
         <v>676</v>
       </c>
       <c r="F145" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4638,16 +4638,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E146">
         <v>680</v>
       </c>
       <c r="F146" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4667,16 +4667,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E147">
         <v>679</v>
       </c>
       <c r="F147" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4695,28 +4695,120 @@
       </c>
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H148" s="2"/>
-      <c r="I148" s="1"/>
-      <c r="J148" s="2"/>
-      <c r="K148" s="1"/>
+      <c r="D148" t="s">
+        <v>38</v>
+      </c>
+      <c r="E148">
+        <v>678</v>
+      </c>
+      <c r="F148" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J148" s="2">
+        <v>5.8333333333333336E-3</v>
+      </c>
+      <c r="K148" s="1">
+        <v>46212.770601851851</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H149" s="2"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="2"/>
-      <c r="K149" s="1"/>
+      <c r="D149" t="s">
+        <v>38</v>
+      </c>
+      <c r="E149">
+        <v>680</v>
+      </c>
+      <c r="F149" t="s">
+        <v>40</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J149" s="2">
+        <v>1.0729166666666666E-2</v>
+      </c>
+      <c r="K149" s="1">
+        <v>46212.771296296298</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H150" s="2"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="2"/>
-      <c r="K150" s="1"/>
+      <c r="D150" t="s">
+        <v>38</v>
+      </c>
+      <c r="E150">
+        <v>676</v>
+      </c>
+      <c r="F150" t="s">
+        <v>42</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J150" s="2">
+        <v>0</v>
+      </c>
+      <c r="K150" s="1">
+        <v>46212.771296296298</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H151" s="2"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="2"/>
-      <c r="K151" s="1"/>
+      <c r="D151" t="s">
+        <v>38</v>
+      </c>
+      <c r="E151">
+        <v>679</v>
+      </c>
+      <c r="F151" t="s">
+        <v>43</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J151" s="2">
+        <v>8.8425925925925929E-3</v>
+      </c>
+      <c r="K151" s="1">
+        <v>46212.771990740737</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H152" s="2"/>
@@ -42289,7 +42381,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE670781-5C46-4273-83A9-0FF7A453CDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F860884B-7048-49F6-A488-E9B676313803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,7 +86,25 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>DNU-Scene of an Accident</t>
+  </si>
+  <si>
+    <t>DNU-NEW-Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Backing Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,13 +119,13 @@
     <t>Distracted Driving</t>
   </si>
   <si>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Micro-Learn Space Mangement</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
@@ -116,28 +134,16 @@
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
+  </si>
+  <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Scene of an Accident</t>
-  </si>
-  <si>
-    <t>DNU-NEW-Vehicle Inspections</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
@@ -174,12 +180,6 @@
   </si>
   <si>
     <t>Alex Kleck</t>
-  </si>
-  <si>
-    <t>Backing Commercial Vehicles</t>
-  </si>
-  <si>
-    <t>Micro-Learn Space Mangement</t>
   </si>
 </sst>
 </file>
@@ -553,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -602,16 +602,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2">
         <v>678</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -631,16 +631,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>680</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -660,16 +660,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4">
         <v>677</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -689,16 +689,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>676</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -718,16 +718,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>679</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -747,16 +747,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>678</v>
       </c>
       <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -776,16 +776,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8">
         <v>680</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -805,16 +805,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9">
         <v>677</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -834,16 +834,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>676</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -863,16 +863,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E11">
         <v>679</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -892,16 +892,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E12">
         <v>678</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -921,16 +921,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13">
         <v>680</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -950,16 +950,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>677</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -979,16 +979,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15">
         <v>676</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1008,16 +1008,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E16">
         <v>679</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1037,16 +1037,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E17">
         <v>678</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>12</v>
@@ -1070,21 +1070,21 @@
       <c r="J18" s="2"/>
       <c r="K18" s="1"/>
       <c r="M18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E19">
         <v>680</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1104,16 +1104,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E20">
         <v>677</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1133,16 +1133,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>676</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1162,16 +1162,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E22">
         <v>679</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1191,16 +1191,16 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E23">
         <v>2168</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1220,16 +1220,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>2168</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1249,16 +1249,16 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E25">
         <v>678</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>679</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E27">
         <v>2168</v>
       </c>
       <c r="F27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1336,16 +1336,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>678</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1365,16 +1365,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E29">
         <v>680</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E30">
         <v>677</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1423,16 +1423,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E31">
         <v>676</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1452,16 +1452,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E32">
         <v>679</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1481,16 +1481,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E33">
         <v>2168</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1510,16 +1510,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E34">
         <v>678</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1539,16 +1539,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E35">
         <v>680</v>
       </c>
       <c r="F35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1568,16 +1568,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>677</v>
       </c>
       <c r="F36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E37">
         <v>676</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1626,16 +1626,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E38">
         <v>679</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1655,16 +1655,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E39">
         <v>2168</v>
       </c>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1684,16 +1684,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E40">
         <v>678</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E41">
         <v>680</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1742,16 +1742,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E42">
         <v>677</v>
       </c>
       <c r="F42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1771,16 +1771,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E43">
         <v>676</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1800,16 +1800,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E44">
         <v>679</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1829,16 +1829,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E45">
         <v>2168</v>
       </c>
       <c r="F45" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1858,16 +1858,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E46">
         <v>678</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1887,16 +1887,16 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E47">
         <v>680</v>
       </c>
       <c r="F47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1916,16 +1916,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E48">
         <v>677</v>
       </c>
       <c r="F48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1945,16 +1945,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E49">
         <v>676</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E50">
         <v>679</v>
       </c>
       <c r="F50" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2003,16 +2003,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E51">
         <v>2168</v>
       </c>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E52">
         <v>678</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2061,16 +2061,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E53">
         <v>680</v>
       </c>
       <c r="F53" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -2090,16 +2090,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E54">
         <v>677</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2119,16 +2119,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E55">
         <v>676</v>
       </c>
       <c r="F55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2148,16 +2148,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E56">
         <v>679</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2177,16 +2177,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E57">
         <v>2168</v>
       </c>
       <c r="F57" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>12</v>
@@ -2210,21 +2210,21 @@
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
       <c r="M58" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E59">
         <v>678</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2244,16 +2244,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E60">
         <v>680</v>
       </c>
       <c r="F60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2273,16 +2273,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E61">
         <v>677</v>
       </c>
       <c r="F61" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2302,16 +2302,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E62">
         <v>676</v>
       </c>
       <c r="F62" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2331,16 +2331,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E63">
         <v>679</v>
       </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2360,16 +2360,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E64">
         <v>2168</v>
       </c>
       <c r="F64" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2389,16 +2389,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E65">
         <v>678</v>
       </c>
       <c r="F65" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2418,16 +2418,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E66">
         <v>680</v>
       </c>
       <c r="F66" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2447,16 +2447,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E67">
         <v>677</v>
       </c>
       <c r="F67" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2476,16 +2476,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E68">
         <v>676</v>
       </c>
       <c r="F68" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2505,16 +2505,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E69">
         <v>679</v>
       </c>
       <c r="F69" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E70">
         <v>2168</v>
       </c>
       <c r="F70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2563,16 +2563,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E71">
         <v>678</v>
       </c>
       <c r="F71" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2592,16 +2592,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E72">
         <v>680</v>
       </c>
       <c r="F72" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2621,16 +2621,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E73">
         <v>677</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2650,16 +2650,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E74">
         <v>676</v>
       </c>
       <c r="F74" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E75">
         <v>679</v>
       </c>
       <c r="F75" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2708,16 +2708,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E76">
         <v>2168</v>
       </c>
       <c r="F76" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2737,16 +2737,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E77">
         <v>678</v>
       </c>
       <c r="F77" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2766,16 +2766,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E78">
         <v>680</v>
       </c>
       <c r="F78" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2795,16 +2795,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E79">
         <v>677</v>
       </c>
       <c r="F79" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2824,16 +2824,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E80">
         <v>676</v>
       </c>
       <c r="F80" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2853,16 +2853,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E81">
         <v>679</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2882,16 +2882,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E82">
         <v>2168</v>
       </c>
       <c r="F82" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2911,16 +2911,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E83">
         <v>678</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2940,16 +2940,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E84">
         <v>680</v>
       </c>
       <c r="F84" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2969,16 +2969,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E85">
         <v>677</v>
       </c>
       <c r="F85" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E86">
         <v>676</v>
       </c>
       <c r="F86" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -3027,16 +3027,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E87">
         <v>679</v>
       </c>
       <c r="F87" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3056,16 +3056,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E88">
         <v>2168</v>
       </c>
       <c r="F88" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3085,16 +3085,16 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E89">
         <v>678</v>
       </c>
       <c r="F89" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E90">
         <v>680</v>
       </c>
       <c r="F90" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3143,16 +3143,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E91">
         <v>677</v>
       </c>
       <c r="F91" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3172,16 +3172,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E92">
         <v>676</v>
       </c>
       <c r="F92" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3201,16 +3201,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E93">
         <v>679</v>
       </c>
       <c r="F93" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3230,16 +3230,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E94">
         <v>2168</v>
       </c>
       <c r="F94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3259,16 +3259,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E95">
         <v>678</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3288,16 +3288,16 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E96">
         <v>680</v>
       </c>
       <c r="F96" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3317,16 +3317,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E97">
         <v>677</v>
       </c>
       <c r="F97" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3346,16 +3346,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E98">
         <v>676</v>
       </c>
       <c r="F98" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3375,16 +3375,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E99">
         <v>679</v>
       </c>
       <c r="F99" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3404,16 +3404,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E100">
         <v>2168</v>
       </c>
       <c r="F100" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3433,16 +3433,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E101">
         <v>678</v>
       </c>
       <c r="F101" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E102">
         <v>680</v>
       </c>
       <c r="F102" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3491,16 +3491,16 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E103">
         <v>677</v>
       </c>
       <c r="F103" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3520,16 +3520,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E104">
         <v>676</v>
       </c>
       <c r="F104" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3549,16 +3549,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E105">
         <v>679</v>
       </c>
       <c r="F105" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3578,16 +3578,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E106">
         <v>2168</v>
       </c>
       <c r="F106" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3607,16 +3607,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E107">
         <v>678</v>
       </c>
       <c r="F107" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3636,16 +3636,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E108">
         <v>680</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3665,16 +3665,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E109">
         <v>677</v>
       </c>
       <c r="F109" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E110">
         <v>676</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3723,16 +3723,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E111">
         <v>679</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3752,16 +3752,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E112">
         <v>2168</v>
       </c>
       <c r="F112" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3781,16 +3781,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E113">
         <v>678</v>
       </c>
       <c r="F113" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3810,16 +3810,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E114">
         <v>680</v>
       </c>
       <c r="F114" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -3839,16 +3839,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E115">
         <v>677</v>
       </c>
       <c r="F115" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3868,16 +3868,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E116">
         <v>676</v>
       </c>
       <c r="F116" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3897,16 +3897,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E117">
         <v>679</v>
       </c>
       <c r="F117" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>12</v>
@@ -3930,21 +3930,21 @@
       <c r="J118" s="2"/>
       <c r="K118" s="1"/>
       <c r="M118" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E119">
         <v>678</v>
       </c>
       <c r="F119" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3964,16 +3964,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E120">
         <v>680</v>
       </c>
       <c r="F120" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3993,16 +3993,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E121">
         <v>676</v>
       </c>
       <c r="F121" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -4022,16 +4022,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E122">
         <v>679</v>
       </c>
       <c r="F122" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -4051,16 +4051,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E123">
         <v>678</v>
       </c>
       <c r="F123" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4080,16 +4080,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E124">
         <v>680</v>
       </c>
       <c r="F124" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4109,16 +4109,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E125">
         <v>676</v>
       </c>
       <c r="F125" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4138,16 +4138,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E126">
         <v>679</v>
       </c>
       <c r="F126" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>14</v>
@@ -4171,21 +4171,21 @@
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
       <c r="M127" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E128">
         <v>678</v>
       </c>
       <c r="F128" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>10</v>
@@ -4205,16 +4205,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E129">
         <v>680</v>
       </c>
       <c r="F129" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4234,16 +4234,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E130">
         <v>676</v>
       </c>
       <c r="F130" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4263,16 +4263,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E131">
         <v>679</v>
       </c>
       <c r="F131" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>14</v>
@@ -4296,21 +4296,21 @@
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
       <c r="M132" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E133">
         <v>678</v>
       </c>
       <c r="F133" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4330,16 +4330,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E134">
         <v>680</v>
       </c>
       <c r="F134" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4359,16 +4359,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E135">
         <v>676</v>
       </c>
       <c r="F135" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4388,16 +4388,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E136">
         <v>679</v>
       </c>
       <c r="F136" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4417,16 +4417,16 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E137">
         <v>678</v>
       </c>
       <c r="F137" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4446,16 +4446,16 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E138">
         <v>680</v>
       </c>
       <c r="F138" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4475,16 +4475,16 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E139">
         <v>676</v>
       </c>
       <c r="F139" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>12</v>
@@ -4508,21 +4508,21 @@
       <c r="J140" s="2"/>
       <c r="K140" s="1"/>
       <c r="M140" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E141">
         <v>679</v>
       </c>
       <c r="F141" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>12</v>
@@ -4546,21 +4546,21 @@
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
       <c r="M142" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E143">
         <v>678</v>
       </c>
       <c r="F143" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4580,16 +4580,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E144">
         <v>680</v>
       </c>
       <c r="F144" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4609,16 +4609,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E145">
         <v>676</v>
       </c>
       <c r="F145" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4638,16 +4638,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E146">
         <v>680</v>
       </c>
       <c r="F146" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4667,16 +4667,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E147">
         <v>679</v>
       </c>
       <c r="F147" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4696,16 +4696,16 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E148">
         <v>678</v>
       </c>
       <c r="F148" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>10</v>
@@ -4725,16 +4725,16 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E149">
         <v>680</v>
       </c>
       <c r="F149" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4754,22 +4754,22 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E150">
         <v>676</v>
       </c>
       <c r="F150" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J150" s="2">
-        <v>0</v>
+        <v>5.7870370370370367E-3</v>
       </c>
       <c r="K150" s="1">
         <v>46212.771296296298</v>
@@ -4783,16 +4783,16 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E151">
         <v>679</v>
       </c>
       <c r="F151" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -12071,6 +12071,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -15394,6 +15395,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -15404,14 +15406,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -15437,6 +15442,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -15446,9 +15452,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -42386,6 +42394,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -42393,6 +42402,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -42400,6 +42410,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -42415,6 +42426,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -42424,6 +42436,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -42431,9 +42444,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -42441,12 +42460,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -42454,12 +42476,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -42471,9 +42496,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -42488,6 +42515,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -42514,6 +42542,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -42524,7 +42553,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -42532,6 +42566,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -42543,6 +42578,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -42550,6 +42586,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -42564,13 +42601,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -42581,15 +42624,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -42605,6 +42651,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -42623,6 +42670,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -42634,6 +42682,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -42651,18 +42700,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -42691,6 +42745,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -42698,9 +42753,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -42723,12 +42780,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -42743,9 +42803,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -42761,12 +42823,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -42787,6 +42851,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -42798,9 +42863,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -42812,6 +42879,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -42851,9 +42919,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -42861,9 +42931,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -42874,6 +42946,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -42881,18 +42954,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -42900,6 +42981,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -42910,6 +42992,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -42936,15 +43019,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -42966,6 +43053,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -42973,9 +43061,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -42983,6 +43073,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -42994,6 +43085,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -43008,6 +43100,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -43017,6 +43113,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -43028,6 +43125,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -43038,10 +43136,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -43049,6 +43152,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -43063,6 +43167,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -43085,6 +43190,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -43104,25 +43210,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -43130,6 +43248,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -43137,15 +43256,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -43159,6 +43285,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -43177,9 +43304,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -43187,9 +43316,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -43197,6 +43328,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -43213,10 +43345,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C13ECA0-6891-4B74-B147-8493700998B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{666C88F1-7B5F-473A-8587-92C96328BAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="48">
   <si>
     <t>Company Name</t>
   </si>
@@ -146,13 +146,16 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
+    <t>Dangers of Distracted Driving</t>
+  </si>
+  <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>3 points of contact</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
@@ -553,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -568,47 +571,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>678</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -629,15 +632,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>680</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -658,15 +661,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>677</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -687,15 +690,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5">
         <v>676</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -716,15 +719,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>679</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -745,18 +748,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>678</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -774,18 +777,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>680</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -803,18 +806,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>677</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -832,18 +835,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>676</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -861,18 +864,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>679</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -890,15 +893,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>678</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
@@ -919,15 +922,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <v>680</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
@@ -948,15 +951,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>677</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
@@ -977,15 +980,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>676</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
@@ -1006,15 +1009,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>679</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
@@ -1037,13 +1040,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>678</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -1074,13 +1077,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>680</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -1103,13 +1106,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>677</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -1132,13 +1135,13 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>676</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -1161,13 +1164,13 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>679</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -1190,13 +1193,13 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23">
         <v>2168</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -1219,13 +1222,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24">
         <v>2168</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1248,13 +1251,13 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25">
         <v>678</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1277,13 +1280,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>679</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
@@ -1306,13 +1309,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>2168</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -1335,13 +1338,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>678</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s">
         <v>24</v>
@@ -1364,13 +1367,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>680</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
         <v>24</v>
@@ -1393,13 +1396,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>677</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s">
         <v>24</v>
@@ -1422,13 +1425,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31">
         <v>676</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>24</v>
@@ -1451,13 +1454,13 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32">
         <v>679</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
         <v>24</v>
@@ -1480,13 +1483,13 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>2168</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -1509,13 +1512,13 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>678</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -1538,13 +1541,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35">
         <v>680</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -1567,13 +1570,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>677</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -1596,13 +1599,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37">
         <v>676</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -1625,13 +1628,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38">
         <v>679</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -1654,13 +1657,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39">
         <v>2168</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F39" t="s">
         <v>22</v>
@@ -1683,13 +1686,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40">
         <v>678</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
         <v>22</v>
@@ -1712,13 +1715,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C41">
         <v>680</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F41" t="s">
         <v>22</v>
@@ -1741,13 +1744,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C42">
         <v>677</v>
       </c>
       <c r="D42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F42" t="s">
         <v>22</v>
@@ -1770,13 +1773,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C43">
         <v>676</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F43" t="s">
         <v>22</v>
@@ -1799,13 +1802,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44">
         <v>679</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F44" t="s">
         <v>22</v>
@@ -1828,13 +1831,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <v>2168</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F45" t="s">
         <v>23</v>
@@ -1857,13 +1860,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C46">
         <v>678</v>
       </c>
       <c r="D46" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
         <v>23</v>
@@ -1886,13 +1889,13 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C47">
         <v>680</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F47" t="s">
         <v>23</v>
@@ -1915,13 +1918,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C48">
         <v>677</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
         <v>23</v>
@@ -1944,13 +1947,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C49">
         <v>676</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F49" t="s">
         <v>23</v>
@@ -1973,13 +1976,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C50">
         <v>679</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F50" t="s">
         <v>23</v>
@@ -2002,16 +2005,16 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C51">
         <v>2168</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2031,16 +2034,16 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C52">
         <v>678</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2060,16 +2063,16 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C53">
         <v>680</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2089,16 +2092,16 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C54">
         <v>677</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2118,16 +2121,16 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C55">
         <v>676</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2147,16 +2150,16 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C56">
         <v>679</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
         <v>10</v>
@@ -2176,16 +2179,16 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C57">
         <v>2168</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -2213,16 +2216,16 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C59">
         <v>678</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F59" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2242,16 +2245,16 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C60">
         <v>680</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F60" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2271,16 +2274,16 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C61">
         <v>677</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s">
         <v>10</v>
@@ -2300,16 +2303,16 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C62">
         <v>676</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2329,16 +2332,16 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63">
         <v>679</v>
       </c>
       <c r="D63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2358,13 +2361,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C64">
         <v>2168</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F64" t="s">
         <v>20</v>
@@ -2387,13 +2390,13 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C65">
         <v>678</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F65" t="s">
         <v>20</v>
@@ -2416,13 +2419,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C66">
         <v>680</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F66" t="s">
         <v>20</v>
@@ -2445,13 +2448,13 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C67">
         <v>677</v>
       </c>
       <c r="D67" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F67" t="s">
         <v>20</v>
@@ -2474,13 +2477,13 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C68">
         <v>676</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F68" t="s">
         <v>20</v>
@@ -2503,13 +2506,13 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>679</v>
       </c>
       <c r="D69" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F69" t="s">
         <v>20</v>
@@ -2532,13 +2535,13 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C70">
         <v>2168</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
@@ -2561,13 +2564,13 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C71">
         <v>678</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
@@ -2590,13 +2593,13 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C72">
         <v>680</v>
       </c>
       <c r="D72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
@@ -2619,13 +2622,13 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C73">
         <v>677</v>
       </c>
       <c r="D73" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
@@ -2648,13 +2651,13 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C74">
         <v>676</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
@@ -2677,13 +2680,13 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C75">
         <v>679</v>
       </c>
       <c r="D75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
@@ -2706,13 +2709,13 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C76">
         <v>2168</v>
       </c>
       <c r="D76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F76" t="s">
         <v>27</v>
@@ -2735,13 +2738,13 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C77">
         <v>678</v>
       </c>
       <c r="D77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F77" t="s">
         <v>27</v>
@@ -2764,13 +2767,13 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C78">
         <v>680</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F78" t="s">
         <v>27</v>
@@ -2793,13 +2796,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C79">
         <v>677</v>
       </c>
       <c r="D79" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F79" t="s">
         <v>27</v>
@@ -2822,13 +2825,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C80">
         <v>676</v>
       </c>
       <c r="D80" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F80" t="s">
         <v>27</v>
@@ -2851,13 +2854,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C81">
         <v>679</v>
       </c>
       <c r="D81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F81" t="s">
         <v>27</v>
@@ -2880,13 +2883,13 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C82">
         <v>2168</v>
       </c>
       <c r="D82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -2909,13 +2912,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C83">
         <v>678</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -2938,13 +2941,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C84">
         <v>680</v>
       </c>
       <c r="D84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -2967,13 +2970,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C85">
         <v>677</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -2996,13 +2999,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C86">
         <v>676</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -3025,13 +3028,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C87">
         <v>679</v>
       </c>
       <c r="D87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -3054,13 +3057,13 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C88">
         <v>2168</v>
       </c>
       <c r="D88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F88" t="s">
         <v>21</v>
@@ -3083,13 +3086,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C89">
         <v>678</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" t="s">
         <v>21</v>
@@ -3112,13 +3115,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C90">
         <v>680</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F90" t="s">
         <v>21</v>
@@ -3141,13 +3144,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C91">
         <v>677</v>
       </c>
       <c r="D91" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F91" t="s">
         <v>21</v>
@@ -3170,13 +3173,13 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C92">
         <v>676</v>
       </c>
       <c r="D92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F92" t="s">
         <v>21</v>
@@ -3199,13 +3202,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C93">
         <v>679</v>
       </c>
       <c r="D93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F93" t="s">
         <v>21</v>
@@ -3228,16 +3231,16 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C94">
         <v>2168</v>
       </c>
       <c r="D94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G94" t="s">
         <v>10</v>
@@ -3257,16 +3260,16 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C95">
         <v>678</v>
       </c>
       <c r="D95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F95" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G95" t="s">
         <v>10</v>
@@ -3286,16 +3289,16 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C96">
         <v>680</v>
       </c>
       <c r="D96" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G96" t="s">
         <v>10</v>
@@ -3315,16 +3318,16 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C97">
         <v>677</v>
       </c>
       <c r="D97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G97" t="s">
         <v>13</v>
@@ -3344,16 +3347,16 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C98">
         <v>676</v>
       </c>
       <c r="D98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G98" t="s">
         <v>10</v>
@@ -3373,16 +3376,16 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C99">
         <v>679</v>
       </c>
       <c r="D99" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F99" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G99" t="s">
         <v>10</v>
@@ -3402,13 +3405,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C100">
         <v>2168</v>
       </c>
       <c r="D100" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F100" t="s">
         <v>29</v>
@@ -3431,13 +3434,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C101">
         <v>678</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F101" t="s">
         <v>29</v>
@@ -3460,13 +3463,13 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C102">
         <v>680</v>
       </c>
       <c r="D102" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F102" t="s">
         <v>29</v>
@@ -3489,13 +3492,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C103">
         <v>677</v>
       </c>
       <c r="D103" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F103" t="s">
         <v>29</v>
@@ -3518,13 +3521,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C104">
         <v>676</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F104" t="s">
         <v>29</v>
@@ -3547,13 +3550,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C105">
         <v>679</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F105" t="s">
         <v>29</v>
@@ -3576,13 +3579,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C106">
         <v>2168</v>
       </c>
       <c r="D106" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F106" t="s">
         <v>37</v>
@@ -3605,13 +3608,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C107">
         <v>678</v>
       </c>
       <c r="D107" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F107" t="s">
         <v>37</v>
@@ -3634,13 +3637,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C108">
         <v>680</v>
       </c>
       <c r="D108" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F108" t="s">
         <v>37</v>
@@ -3663,13 +3666,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C109">
         <v>677</v>
       </c>
       <c r="D109" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F109" t="s">
         <v>37</v>
@@ -3692,13 +3695,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C110">
         <v>676</v>
       </c>
       <c r="D110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F110" t="s">
         <v>37</v>
@@ -3721,13 +3724,13 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C111">
         <v>679</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F111" t="s">
         <v>37</v>
@@ -3750,13 +3753,13 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C112">
         <v>2168</v>
       </c>
       <c r="D112" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F112" t="s">
         <v>22</v>
@@ -3779,13 +3782,13 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C113">
         <v>678</v>
       </c>
       <c r="D113" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F113" t="s">
         <v>22</v>
@@ -3808,13 +3811,13 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C114">
         <v>680</v>
       </c>
       <c r="D114" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F114" t="s">
         <v>22</v>
@@ -3837,13 +3840,13 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C115">
         <v>677</v>
       </c>
       <c r="D115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F115" t="s">
         <v>22</v>
@@ -3866,13 +3869,13 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C116">
         <v>676</v>
       </c>
       <c r="D116" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F116" t="s">
         <v>22</v>
@@ -3895,13 +3898,13 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C117">
         <v>679</v>
       </c>
       <c r="D117" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F117" t="s">
         <v>22</v>
@@ -3932,13 +3935,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C119">
         <v>678</v>
       </c>
       <c r="D119" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F119" t="s">
         <v>23</v>
@@ -3961,13 +3964,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C120">
         <v>680</v>
       </c>
       <c r="D120" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F120" t="s">
         <v>23</v>
@@ -3990,13 +3993,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C121">
         <v>676</v>
       </c>
       <c r="D121" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F121" t="s">
         <v>23</v>
@@ -4019,13 +4022,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C122">
         <v>679</v>
       </c>
       <c r="D122" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F122" t="s">
         <v>23</v>
@@ -4048,13 +4051,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C123">
         <v>678</v>
       </c>
       <c r="D123" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F123" t="s">
         <v>30</v>
@@ -4077,13 +4080,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C124">
         <v>680</v>
       </c>
       <c r="D124" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F124" t="s">
         <v>30</v>
@@ -4106,13 +4109,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C125">
         <v>676</v>
       </c>
       <c r="D125" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F125" t="s">
         <v>30</v>
@@ -4135,13 +4138,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C126">
         <v>679</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F126" t="s">
         <v>30</v>
@@ -4172,13 +4175,13 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C128">
         <v>678</v>
       </c>
       <c r="D128" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F128" t="s">
         <v>31</v>
@@ -4201,13 +4204,13 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C129">
         <v>680</v>
       </c>
       <c r="D129" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F129" t="s">
         <v>31</v>
@@ -4230,13 +4233,13 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C130">
         <v>676</v>
       </c>
       <c r="D130" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F130" t="s">
         <v>31</v>
@@ -4259,13 +4262,13 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C131">
         <v>679</v>
       </c>
       <c r="D131" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F131" t="s">
         <v>31</v>
@@ -4296,13 +4299,13 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C133">
         <v>678</v>
       </c>
       <c r="D133" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F133" t="s">
         <v>32</v>
@@ -4325,13 +4328,13 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C134">
         <v>680</v>
       </c>
       <c r="D134" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F134" t="s">
         <v>32</v>
@@ -4354,13 +4357,13 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C135">
         <v>676</v>
       </c>
       <c r="D135" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F135" t="s">
         <v>32</v>
@@ -4383,13 +4386,13 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C136">
         <v>679</v>
       </c>
       <c r="D136" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F136" t="s">
         <v>32</v>
@@ -4412,13 +4415,13 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C137">
         <v>678</v>
       </c>
       <c r="D137" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F137" t="s">
         <v>33</v>
@@ -4441,13 +4444,13 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C138">
         <v>680</v>
       </c>
       <c r="D138" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F138" t="s">
         <v>33</v>
@@ -4470,13 +4473,13 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C139">
         <v>676</v>
       </c>
       <c r="D139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F139" t="s">
         <v>33</v>
@@ -4507,13 +4510,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C141">
         <v>679</v>
       </c>
       <c r="D141" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F141" t="s">
         <v>33</v>
@@ -4544,13 +4547,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C143">
         <v>678</v>
       </c>
       <c r="D143" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F143" t="s">
         <v>24</v>
@@ -4573,13 +4576,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C144">
         <v>680</v>
       </c>
       <c r="D144" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F144" t="s">
         <v>24</v>
@@ -4602,13 +4605,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C145">
         <v>676</v>
       </c>
       <c r="D145" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F145" t="s">
         <v>24</v>
@@ -4631,13 +4634,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C146">
         <v>680</v>
       </c>
       <c r="D146" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F146" t="s">
         <v>34</v>
@@ -4660,13 +4663,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C147">
         <v>679</v>
       </c>
       <c r="D147" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F147" t="s">
         <v>34</v>
@@ -4689,13 +4692,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C148">
         <v>678</v>
       </c>
       <c r="D148" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F148" t="s">
         <v>27</v>
@@ -4718,13 +4721,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C149">
         <v>680</v>
       </c>
       <c r="D149" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F149" t="s">
         <v>27</v>
@@ -4747,13 +4750,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C150">
         <v>676</v>
       </c>
       <c r="D150" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F150" t="s">
         <v>27</v>
@@ -4776,13 +4779,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C151">
         <v>679</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F151" t="s">
         <v>27</v>
@@ -4804,28 +4807,120 @@
       </c>
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H152" s="2"/>
-      <c r="I152" s="1"/>
-      <c r="J152" s="2"/>
-      <c r="K152" s="1"/>
+      <c r="B152" t="s">
+        <v>41</v>
+      </c>
+      <c r="C152">
+        <v>678</v>
+      </c>
+      <c r="D152" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" t="s">
+        <v>35</v>
+      </c>
+      <c r="G152" t="s">
+        <v>13</v>
+      </c>
+      <c r="H152" s="2">
+        <v>0</v>
+      </c>
+      <c r="I152" s="1">
+        <v>46237.849768518521</v>
+      </c>
+      <c r="J152" s="2">
+        <v>0</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H153" s="2"/>
-      <c r="I153" s="1"/>
-      <c r="J153" s="2"/>
-      <c r="K153" s="1"/>
+      <c r="B153" t="s">
+        <v>41</v>
+      </c>
+      <c r="C153">
+        <v>680</v>
+      </c>
+      <c r="D153" t="s">
+        <v>43</v>
+      </c>
+      <c r="F153" t="s">
+        <v>35</v>
+      </c>
+      <c r="G153" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" s="2">
+        <v>0</v>
+      </c>
+      <c r="I153" s="1">
+        <v>46237.850462962961</v>
+      </c>
+      <c r="J153" s="2">
+        <v>0</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H154" s="2"/>
-      <c r="I154" s="1"/>
-      <c r="J154" s="2"/>
-      <c r="K154" s="1"/>
+      <c r="B154" t="s">
+        <v>41</v>
+      </c>
+      <c r="C154">
+        <v>676</v>
+      </c>
+      <c r="D154" t="s">
+        <v>45</v>
+      </c>
+      <c r="F154" t="s">
+        <v>35</v>
+      </c>
+      <c r="G154" t="s">
+        <v>10</v>
+      </c>
+      <c r="H154" s="2">
+        <v>5.8217592592592592E-3</v>
+      </c>
+      <c r="I154" s="1">
+        <v>46237.851157407407</v>
+      </c>
+      <c r="J154" s="2">
+        <v>0</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H155" s="2"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="2"/>
-      <c r="K155" s="1"/>
+      <c r="B155" t="s">
+        <v>41</v>
+      </c>
+      <c r="C155">
+        <v>679</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="F155" t="s">
+        <v>35</v>
+      </c>
+      <c r="G155" t="s">
+        <v>13</v>
+      </c>
+      <c r="H155" s="2">
+        <v>0</v>
+      </c>
+      <c r="I155" s="1">
+        <v>46237.851157407407</v>
+      </c>
+      <c r="J155" s="2">
+        <v>0</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H156" s="2"/>
@@ -15531,9 +15626,11 @@
       <c r="K1944" s="1"/>
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1945" s="2"/>
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
       <c r="K1946" s="1"/>
     </row>
@@ -15599,6 +15696,7 @@
       <c r="K1958" s="1"/>
     </row>
     <row r="1959" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1959" s="2"/>
       <c r="I1959" s="1"/>
       <c r="K1959" s="1"/>
     </row>
@@ -15641,6 +15739,7 @@
       <c r="K1966" s="1"/>
     </row>
     <row r="1967" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:11" x14ac:dyDescent="0.25">
@@ -15654,6 +15753,7 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
       <c r="K1970" s="1"/>
     </row>
@@ -15724,6 +15824,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -15753,6 +15854,7 @@
       <c r="K1988" s="1"/>
     </row>
     <row r="1989" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
       <c r="K1989" s="1"/>
     </row>
@@ -15774,6 +15876,7 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -15852,6 +15955,7 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -46033,6 +46137,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -46047,11 +46152,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46062,10 +46169,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -46083,14 +46193,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46101,14 +46214,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -46135,6 +46251,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -46143,6 +46260,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -46155,22 +46273,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46189,6 +46312,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46199,10 +46323,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -46211,10 +46337,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -46228,82 +46356,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -46317,6 +46460,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46327,6 +46471,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -46334,6 +46479,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -46342,86 +46488,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46438,26 +46597,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -46488,6 +46653,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -46497,10 +46663,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -46513,14 +46681,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -46529,14 +46700,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -46555,26 +46729,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46593,6 +46773,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -46601,10 +46782,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -46613,6 +46796,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -46625,10 +46809,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -46637,6 +46823,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -46645,14 +46832,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -46661,14 +46851,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -46685,76 +46878,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -46768,31 +46970,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -46805,10 +47014,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -46817,10 +47028,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -46829,6 +47042,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -46843,10 +47057,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -46855,10 +47071,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -46872,6 +47090,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -46887,14 +47106,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -46912,14 +47134,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -46932,10 +47157,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -46944,14 +47171,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -46960,10 +47190,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -46972,14 +47204,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -47001,6 +47236,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -47009,39 +47245,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{666C88F1-7B5F-473A-8587-92C96328BAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2791794B-1457-4FA9-8740-51AA5EA48CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="48">
   <si>
     <t>Company Name</t>
   </si>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -632,7 +632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -806,7 +806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>41</v>
       </c>
@@ -922,7 +922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>41</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>41</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>41</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>41</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>41</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>41</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>41</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>41</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>41</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -4820,16 +4820,16 @@
         <v>35</v>
       </c>
       <c r="G152" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H152" s="2">
-        <v>0</v>
+        <v>5.5671296296296293E-3</v>
       </c>
       <c r="I152" s="1">
         <v>46237.849768518521</v>
       </c>
       <c r="J152" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>11</v>
@@ -4849,16 +4849,16 @@
         <v>35</v>
       </c>
       <c r="G153" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H153" s="2">
-        <v>0</v>
+        <v>1.1631944444444445E-2</v>
       </c>
       <c r="I153" s="1">
         <v>46237.850462962961</v>
       </c>
       <c r="J153" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" s="1" t="s">
         <v>11</v>
@@ -4907,7 +4907,7 @@
         <v>35</v>
       </c>
       <c r="G155" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>46237.851157407407</v>
       </c>
       <c r="J155" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K155" s="1" t="s">
         <v>11</v>
@@ -4926,7 +4926,9 @@
       <c r="H156" s="2"/>
       <c r="I156" s="1"/>
       <c r="J156" s="2"/>
-      <c r="K156" s="1"/>
+      <c r="K156" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H157" s="2"/>
@@ -5030,7 +5032,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -5060,7 +5062,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5120,7 +5122,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5228,7 +5230,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5420,7 +5422,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -5936,7 +5938,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6002,7 +6004,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6014,7 +6016,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6110,7 +6112,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6122,7 +6124,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6218,7 +6220,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6278,7 +6280,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -15692,6 +15694,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -15729,6 +15732,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -15793,6 +15797,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -15824,11 +15829,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -15839,6 +15844,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -15914,6 +15920,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -15924,6 +15931,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -15955,7 +15963,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -45248,6 +45255,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45540,6 +45548,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -45850,6 +45860,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -45974,6 +45985,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -45985,6 +45997,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46133,6 +46146,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -46143,10 +46157,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -46180,15 +46196,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -46229,18 +46248,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46256,6 +46279,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -46265,10 +46289,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -46304,10 +46330,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -46333,6 +46361,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -46347,6 +46376,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46381,6 +46411,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -46390,6 +46421,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -46399,6 +46431,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -46413,15 +46446,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -46451,6 +46485,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46471,11 +46506,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -46484,6 +46521,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -46513,6 +46551,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -46522,10 +46561,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -46540,14 +46581,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -46567,10 +46611,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -46590,9 +46636,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -46627,18 +46676,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46653,12 +46706,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -46673,10 +46726,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -46696,6 +46751,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -46715,6 +46771,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46724,6 +46781,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -46769,6 +46827,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -46778,6 +46837,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -46792,6 +46852,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -46801,10 +46862,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -46819,6 +46882,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -46828,6 +46892,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -46847,6 +46912,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -46866,10 +46932,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -46879,6 +46947,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -46889,10 +46958,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -46907,18 +46978,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -46938,10 +47013,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -46961,6 +47038,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -46991,7 +47069,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -47006,10 +47083,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -47024,6 +47103,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -47038,11 +47118,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47052,6 +47132,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -47067,6 +47148,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -47081,6 +47163,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47101,6 +47184,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -47126,11 +47210,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -47149,15 +47235,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -47167,6 +47254,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -47186,6 +47274,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -47200,6 +47289,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -47219,10 +47309,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47232,6 +47324,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -47242,6 +47335,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -47278,7 +47372,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -47287,6 +47380,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -47300,10 +47394,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2791794B-1457-4FA9-8740-51AA5EA48CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE5B24F3-3487-4E9E-8F70-13CCCC85B5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -152,16 +152,16 @@
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>DNU-Fatigue</t>
+  </si>
+  <si>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>3 points of contact</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
-  </si>
-  <si>
-    <t>DNU-Fatigue</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>The Electric Light &amp; Power Company</t>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -632,7 +632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -759,7 +759,7 @@
         <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -806,7 +806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>41</v>
       </c>
@@ -817,7 +817,7 @@
         <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -875,7 +875,7 @@
         <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -922,7 +922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>41</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>41</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>41</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2043,7 +2043,7 @@
         <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2072,7 +2072,7 @@
         <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2090,7 +2090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>41</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>44</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2130,7 +2130,7 @@
         <v>45</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2159,7 +2159,7 @@
         <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
         <v>10</v>
@@ -2188,7 +2188,7 @@
         <v>47</v>
       </c>
       <c r="F57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -2225,7 +2225,7 @@
         <v>42</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2254,7 +2254,7 @@
         <v>43</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2283,7 +2283,7 @@
         <v>44</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G61" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2341,7 +2341,7 @@
         <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2649,7 +2649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>41</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>41</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>41</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>47</v>
       </c>
       <c r="F106" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G106" t="s">
         <v>10</v>
@@ -3617,7 +3617,7 @@
         <v>42</v>
       </c>
       <c r="F107" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>43</v>
       </c>
       <c r="F108" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G108" t="s">
         <v>10</v>
@@ -3675,7 +3675,7 @@
         <v>44</v>
       </c>
       <c r="F109" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G109" t="s">
         <v>13</v>
@@ -3704,7 +3704,7 @@
         <v>45</v>
       </c>
       <c r="F110" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G110" t="s">
         <v>10</v>
@@ -3733,7 +3733,7 @@
         <v>46</v>
       </c>
       <c r="F111" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G111" t="s">
         <v>10</v>
@@ -3751,7 +3751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>41</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>41</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -5032,7 +5032,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -5062,7 +5062,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5122,7 +5122,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5230,7 +5230,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5422,7 +5422,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -5938,7 +5938,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6004,7 +6004,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6016,7 +6016,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6112,7 +6112,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6124,7 +6124,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6220,7 +6220,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6280,7 +6280,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -15681,6 +15681,7 @@
       <c r="K1954" s="1"/>
     </row>
     <row r="1955" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
       <c r="K1955" s="1"/>
     </row>
@@ -15690,6 +15691,7 @@
       <c r="K1956" s="1"/>
     </row>
     <row r="1957" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
       <c r="K1957" s="1"/>
     </row>
@@ -15829,6 +15831,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -15882,7 +15885,6 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -45255,7 +45257,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45548,8 +45549,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -45860,7 +45859,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -45985,7 +45983,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -45997,7 +45994,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46146,35 +46142,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46185,44 +46175,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46233,37 +46214,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46274,52 +46248,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46330,17 +46294,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46351,32 +46312,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46386,106 +46341,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46495,7 +46430,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46506,127 +46440,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46636,62 +46544,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46711,67 +46606,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46781,38 +46663,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46827,117 +46702,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -46946,99 +46798,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47048,23 +46881,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -47073,52 +46902,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -47132,38 +46951,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47173,7 +46985,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47184,23 +46995,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47210,37 +47017,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -47249,72 +47049,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47324,76 +47110,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\The-Electric-Light-and-Power-Company\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE5B24F3-3487-4E9E-8F70-13CCCC85B5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD63734C-CE80-46E6-B8D8-B2917B8FC697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -152,16 +152,16 @@
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>DNU-Fatigue</t>
+    <t>Hazcom for CDL Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
   </si>
   <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>The Electric Light &amp; Power Company</t>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -759,7 +759,7 @@
         <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -817,7 +817,7 @@
         <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -875,7 +875,7 @@
         <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2043,7 +2043,7 @@
         <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2072,7 +2072,7 @@
         <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2101,7 +2101,7 @@
         <v>44</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2130,7 +2130,7 @@
         <v>45</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2159,7 +2159,7 @@
         <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
         <v>10</v>
@@ -2188,7 +2188,7 @@
         <v>47</v>
       </c>
       <c r="F57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -2225,7 +2225,7 @@
         <v>42</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2254,7 +2254,7 @@
         <v>43</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2283,7 +2283,7 @@
         <v>44</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2341,7 +2341,7 @@
         <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>47</v>
       </c>
       <c r="F106" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G106" t="s">
         <v>10</v>
@@ -3617,7 +3617,7 @@
         <v>42</v>
       </c>
       <c r="F107" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>43</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G108" t="s">
         <v>10</v>
@@ -3675,7 +3675,7 @@
         <v>44</v>
       </c>
       <c r="F109" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G109" t="s">
         <v>13</v>
@@ -3704,7 +3704,7 @@
         <v>45</v>
       </c>
       <c r="F110" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G110" t="s">
         <v>10</v>
@@ -3733,7 +3733,7 @@
         <v>46</v>
       </c>
       <c r="F111" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G111" t="s">
         <v>10</v>
@@ -45257,6 +45257,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45549,6 +45550,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -45859,6 +45862,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -45983,6 +45987,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -45994,6 +45999,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46142,29 +46148,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46175,35 +46187,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46214,30 +46235,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46248,42 +46276,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46294,14 +46332,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46312,26 +46353,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46341,86 +46388,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46430,6 +46498,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46440,101 +46509,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46544,49 +46639,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46601,59 +46709,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46663,31 +46785,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46697,99 +46826,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -46798,80 +46951,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -46881,67 +47053,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -46951,31 +47139,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -46985,6 +47180,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -46995,19 +47191,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47017,90 +47217,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47110,51 +47332,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
